--- a/data/trans_orig/P32A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455982</t>
+          <t>456986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468315</t>
+          <t>468156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162914</t>
+          <t>163156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>622833</t>
+          <t>623112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635367</t>
+          <t>635641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20609</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1040527</t>
+          <t>1039817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1053358</t>
+          <t>1052809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>526879</t>
+          <t>527766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1571649</t>
+          <t>1571037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1585476</t>
+          <t>1585209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344765</t>
+          <t>344297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187813</t>
+          <t>187615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535754</t>
+          <t>535751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542770</t>
+          <t>542772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1849926</t>
+          <t>1850945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1868000</t>
+          <t>1868939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885575</t>
+          <t>885511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>892575</t>
+          <t>892579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2740243</t>
+          <t>2739237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2759218</t>
+          <t>2759126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>483020</t>
+          <t>482246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500822</t>
+          <t>500573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228118</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712849</t>
+          <t>713141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731227</t>
+          <t>730741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23616</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47303</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56426</t>
+          <t>56920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1146586</t>
+          <t>1144173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1170273</t>
+          <t>1169825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>575109</t>
+          <t>574087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588741</t>
+          <t>588043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1729393</t>
+          <t>1728899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1756242</t>
+          <t>1755076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319820</t>
+          <t>320270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217871</t>
+          <t>217717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541074</t>
+          <t>541045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547681</t>
+          <t>547675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39636</t>
+          <t>38050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79173</t>
+          <t>80244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1960575</t>
+          <t>1960965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1990082</t>
+          <t>1991668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026850</t>
+          <t>1026322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040431</t>
+          <t>1040374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2994991</t>
+          <t>2993920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3027389</t>
+          <t>3027851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>335677</t>
+          <t>335059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350648</t>
+          <t>350718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125599</t>
+          <t>126104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465646</t>
+          <t>465557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482797</t>
+          <t>483161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33968</t>
+          <t>34920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40845</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1220130</t>
+          <t>1219178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1239292</t>
+          <t>1238957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>718067</t>
+          <t>718036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>728462</t>
+          <t>727571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1942831</t>
+          <t>1942605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1964146</t>
+          <t>1964956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>370862</t>
+          <t>370505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263101</t>
+          <t>264280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276371</t>
+          <t>276547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636901</t>
+          <t>639017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651859</t>
+          <t>652535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53914</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>25927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40608</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>72805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1936729</t>
+          <t>1936315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1962960</t>
+          <t>1961503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1118183</t>
+          <t>1117344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1134744</t>
+          <t>1134700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3061482</t>
+          <t>3061109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3093306</t>
+          <t>3091374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225288</t>
+          <t>225147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236607</t>
+          <t>236559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>292425</t>
+          <t>291058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>303381</t>
+          <t>303348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>31983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>962105</t>
+          <t>961900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>975464</t>
+          <t>975476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686143</t>
+          <t>686199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>702580</t>
+          <t>702178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1652829</t>
+          <t>1654311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1674535</t>
+          <t>1674594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>330559</t>
+          <t>330531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340333</t>
+          <t>340058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233806</t>
+          <t>233594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239907</t>
+          <t>239854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568196</t>
+          <t>567128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578801</t>
+          <t>579049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56669</t>
+          <t>56466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1528412</t>
+          <t>1527730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1547284</t>
+          <t>1547815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>989568</t>
+          <t>989247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1006893</t>
+          <t>1007113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2524340</t>
+          <t>2524543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2551407</t>
+          <t>2550891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>7606</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>3832</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>16514</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4379</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>7606</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>15416</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456986</t>
+          <t>456978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468156</t>
+          <t>468284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>166611</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>162832</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>167535</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>630922</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>622014</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>634696</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>166611</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>163156</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>167535</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>630922</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>623112</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>635641</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1039817</t>
+          <t>1040341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1052809</t>
+          <t>1052762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>527766</t>
+          <t>527380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1571037</t>
+          <t>1570863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1585209</t>
+          <t>1585409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344297</t>
+          <t>344608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187615</t>
+          <t>187564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535751</t>
+          <t>536015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542772</t>
+          <t>542781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1850945</t>
+          <t>1851211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1868939</t>
+          <t>1868558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885511</t>
+          <t>885493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>892579</t>
+          <t>892575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2739237</t>
+          <t>2738894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2759126</t>
+          <t>2759023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>27472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482246</t>
+          <t>482162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500573</t>
+          <t>501017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713141</t>
+          <t>712118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730741</t>
+          <t>730971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49716</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56920</t>
+          <t>61021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1144173</t>
+          <t>1146703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169825</t>
+          <t>1170794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>574087</t>
+          <t>575565</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588043</t>
+          <t>587932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1728899</t>
+          <t>1724798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1755076</t>
+          <t>1755446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320270</t>
+          <t>319337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217717</t>
+          <t>217319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541045</t>
+          <t>540865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547675</t>
+          <t>547667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38050</t>
+          <t>39006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68753</t>
+          <t>70503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46313</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80244</t>
+          <t>79347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1960965</t>
+          <t>1959215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1991668</t>
+          <t>1990712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026322</t>
+          <t>1027220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040374</t>
+          <t>1040624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2993920</t>
+          <t>2994817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3027851</t>
+          <t>3027981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>335059</t>
+          <t>335592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350718</t>
+          <t>350434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126104</t>
+          <t>124955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465557</t>
+          <t>466105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483161</t>
+          <t>483047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>34608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>40985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1219178</t>
+          <t>1219490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1238957</t>
+          <t>1239575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>718036</t>
+          <t>717984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>727571</t>
+          <t>727556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1942605</t>
+          <t>1942691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1964956</t>
+          <t>1964771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>370505</t>
+          <t>370275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264280</t>
+          <t>263841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276547</t>
+          <t>276609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639017</t>
+          <t>639154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652535</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54328</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25927</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72805</t>
+          <t>73571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1936315</t>
+          <t>1936357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1961503</t>
+          <t>1961539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1117344</t>
+          <t>1117761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1134700</t>
+          <t>1134506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3061109</t>
+          <t>3060343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3091374</t>
+          <t>3091853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18109</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>232041</t>
+          <t>246651</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225147</t>
+          <t>239450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236559</t>
+          <t>250944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,27 +5685,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>298520</t>
+          <t>320697</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>291058</t>
+          <t>314069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>303348</t>
+          <t>325717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>970468</t>
+          <t>1029011</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>961900</t>
+          <t>1020631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>975476</t>
+          <t>1034407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>695509</t>
+          <t>541154</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686199</t>
+          <t>529574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>702178</t>
+          <t>547857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1665977</t>
+          <t>1570165</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1654311</t>
+          <t>1557838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1674594</t>
+          <t>1579740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>705219</t>
+          <t>555253</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>705219</t>
+          <t>555253</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>705219</t>
+          <t>555253</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1686294</t>
+          <t>1595900</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1686294</t>
+          <t>1595900</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1686294</t>
+          <t>1595900</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>336773</t>
+          <t>358973</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>330531</t>
+          <t>352728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340058</t>
+          <t>362988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>237654</t>
+          <t>260481</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233594</t>
+          <t>255560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239854</t>
+          <t>263337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>574427</t>
+          <t>619453</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567128</t>
+          <t>611781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579049</t>
+          <t>624423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>41208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56466</t>
+          <t>65054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1539282</t>
+          <t>1634633</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1527730</t>
+          <t>1623861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1547815</t>
+          <t>1643330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>999643</t>
+          <t>875680</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>989247</t>
+          <t>863445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1007113</t>
+          <t>883526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2538925</t>
+          <t>2510315</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2524543</t>
+          <t>2495071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2550891</t>
+          <t>2523322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1013739</t>
+          <t>895055</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1013739</t>
+          <t>895055</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1013739</t>
+          <t>895055</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2581009</t>
+          <t>2560125</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2581009</t>
+          <t>2560125</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2581009</t>
+          <t>2560125</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
